--- a/uploads/sailup_per_questions_chatgpt_input_output.xlsx
+++ b/uploads/sailup_per_questions_chatgpt_input_output.xlsx
@@ -487,16 +487,16 @@
         <v>Pieza de acero moldeada que firme en cubierta sirve para dirigir los cabos en un sentido determinado.</v>
       </c>
       <c r="M2" t="str">
-        <v>Una embarcación está &lt;strong&gt;adrizada&lt;/strong&gt; cuando navega vertical y equilibrada, sin inclinación lateral respecto a la vertical; en otras palabras, sin escora.</v>
+        <v>Una bita es un elemento fundamental en la navegación, ya que se trata de una pieza cilíndrica fijada a la cubierta de la embarcación, utilizada para asegurar los cabos durante el amarre. Su diseño permite que los marineros puedan sujetar las cuerdas de manera segura, facilitando así el manejo de la embarcación en puerto.</v>
       </c>
       <c r="N2" t="str">
-        <v>Se dice que una embarcación &lt;strong&gt;está en varadero&lt;/strong&gt; cuando ha sido sacada del agua y se encuentra en tierra, en un astillero o dique, para realizar trabajos de mantenimiento, reparación o invernaje.</v>
+        <v>Una bita es un elemento de amarre que se utiliza en los muelles para asegurar las embarcaciones. Su función principal es proporcionar un punto de sujeción robusto donde se pueden atar las cuerdas de los barcos, garantizando así su estabilidad en el puerto.</v>
       </c>
       <c r="O2" t="str">
-        <v>En náutica, la expresión &lt;strong&gt;apenas se mueve&lt;/strong&gt; indica que el barco lleva una arrancada muy pequeña o casi nula, es decir, prácticamente no avanza con respecto al agua.</v>
+        <v>Una bita es un elemento de amarre en las embarcaciones, generalmente en forma de T, que se utiliza para asegurar cabos y cuerdas en la cubierta. Su función principal es proporcionar un punto de anclaje seguro para mantener la estabilidad de la embarcación durante las maniobras.</v>
       </c>
       <c r="P2" t="str">
-        <v>Una embarcación &lt;strong&gt;navega contra el viento&lt;/strong&gt; cuando avanza en dirección al viento o lo más cercano posible a él, lo que implica mayor resistencia y necesidad de ajustar el gobierno.</v>
+        <v>Una bita es un elemento de amarre que se utiliza en la cubierta de las embarcaciones para asegurar cabos y cuerdas. Su diseño permite que los cabos se dirijan en una dirección específica, facilitando así la maniobra y el control de las velas y otros elementos del barco.</v>
       </c>
     </row>
     <row r="3">
@@ -537,16 +537,16 @@
         <v>El medio nudo alrededor de una verga.</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>La gaza de un cabo es un nudo que se forma en el extremo de una cuerda, donde se trenzan los cordones sobre el firme, creando un lazo que permite asegurar o sujetar objetos de manera efectiva. Este tipo de nudo es fundamental en la navegación, ya que proporciona una conexión segura y confiable en diversas maniobras a bordo.</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>La curvatura de un cabo entre los extremos se refiere a la forma en que se presenta el cabo cuando está tenso o en uso. Este fenómeno puede influir en la manera en que se distribuye la carga y en la eficacia del nudo que se utilice.</v>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>La definición proporcionada se refiere al nudo de gaza, que es un tipo de nudo utilizado para hacer un lazo en un cabo. Este nudo es útil para asegurar objetos o para crear un punto de anclaje en diversas maniobras a bordo.</v>
       </c>
       <c r="P3" t="str">
-        <v/>
+        <v>La gaza de un cabo es un tipo de nudo que se utiliza para formar un lazo en el extremo de una cuerda, permitiendo que se sujete a un objeto o se pase por una polea. Este nudo es fundamental en la navegación, ya que proporciona una conexión segura y ajustable.</v>
       </c>
     </row>
     <row r="4">
@@ -587,16 +587,16 @@
         <v>Pieza de madera o metal que sale del casco horizontalmente</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>El bichero es una herramienta náutica que consiste en una vara con un herraje en un extremo, utilizada principalmente para el amarre de embarcaciones. Su diseño permite al navegante alcanzar y manipular las líneas de amarre desde una distancia segura, facilitando así el atraque y desatraque de la embarcación.</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>El término "bichero" se refiere a una herramienta utilizada en la navegación, que consiste en un palo largo con un gancho en su extremo, diseñado para ayudar a atrapar o sujetar objetos en el agua, como una boya o una línea. Es un utensilio muy útil para maniobras en puerto o al acercarse a la costa.</v>
       </c>
       <c r="O4" t="str">
-        <v/>
+        <v>El término "bichero" se refiere a una herramienta utilizada en la navegación, que consiste en un palo largo con un gancho en su extremo, diseñado para ayudar a atrapar o sujetar objetos en el agua, como una boya o una línea. Es un utensilio muy útil para maniobras en puerto o al acercarse a la costa.</v>
       </c>
       <c r="P4" t="str">
-        <v/>
+        <v>El término "bichero" se refiere a una herramienta utilizada en la navegación, que consiste en un palo largo con un gancho en su extremo, diseñado para ayudar a atrapar o sujetar objetos en el agua, como una boya o una línea. Es fundamental para maniobras de amarre y para la seguridad en la embarcación.</v>
       </c>
     </row>
     <row r="5">
@@ -637,16 +637,16 @@
         <v>Superficie porosa apta para la limpieza de los instrumentos de precisión.</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>La gaza es una técnica de nudos que consiste en hacer un lazo en el extremo de un cabo, permitiendo asegurar el cabo o enganchar otros elementos. Este nudo es fundamental en la navegación, ya que proporciona una forma segura de fijar o sujetar objetos a bordo.</v>
       </c>
       <c r="N5" t="str">
-        <v/>
+        <v>La gaza es un tipo de cabo que se utiliza para asegurar o manipular el ancla, permitiendo su izado o fondeo de manera eficiente. Este elemento es fundamental en la navegación, ya que garantiza la seguridad de la embarcación al mantener el ancla en su lugar.</v>
       </c>
       <c r="O5" t="str">
-        <v/>
+        <v>La gaza es un término que se refiere a una parte de la jarcia, específicamente a un cabo que se utiliza para sostener o ajustar las velas en una embarcación. Su correcta utilización es fundamental para el manejo eficiente de las velas y el control del barco.</v>
       </c>
       <c r="P5" t="str">
-        <v/>
+        <v>La gaza es un tipo de cabo que se utiliza para realizar nudos o para asegurar elementos en la embarcación. Su diseño permite que sea flexible y resistente, lo que la hace ideal para diversas aplicaciones en la navegación.</v>
       </c>
     </row>
     <row r="6">
@@ -737,16 +737,16 @@
         <v>Es el cabo que une un muerto con su boya en la superficie.</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>Un bichero es una herramienta náutica que consiste en una pértiga con un gancho y una punta en su extremo, utilizada para atrapar o sujetar objetos en el agua, como boyas o redes. Es especialmente útil en maniobras de amarre y en la pesca, facilitando el manejo de elementos que están fuera del alcance directo.</v>
       </c>
       <c r="N7" t="str">
-        <v/>
+        <v>Un bichero es una herramienta utilizada en la navegación y la pesca, que consiste en un palo largo con una punta en forma de gancho. Su función principal es ayudar a atrapar o sujetar objetos en el agua, como redes o peces, facilitando así las maniobras a bordo.</v>
       </c>
       <c r="O7" t="str">
-        <v/>
+        <v>Un bichero es una herramienta utilizada en la navegación que consiste en un palo largo con una punta en forma de gancho. Su función principal es ayudar a los marineros a atrapar o sujetar objetos en el agua, facilitando el manejo de las embarcaciones en el puerto.</v>
       </c>
       <c r="P7" t="str">
-        <v/>
+        <v>Un bichero es una herramienta utilizada en la navegación que consiste en un palo largo con un gancho en su extremo, diseñado para ayudar a atrapar o manipular objetos en el agua, como boyas o anclas. Su uso es fundamental para facilitar las maniobras en puertos y en la costa.</v>
       </c>
     </row>
     <row r="8">
@@ -887,16 +887,16 @@
         <v>Es un bloque pesado colgado de un flotador que lo sostiene a determinada profundidad.</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>Un muerto es un bloque de hormigón que se encuentra en el fondo marino y se utiliza para amarrar el extremo de un cabo que sostiene una baliza. Este sistema de anclaje es fundamental para la señalización marítima, ya que asegura que las balizas permanezcan en su lugar y sean visibles para la navegación.</v>
       </c>
       <c r="N10" t="str">
-        <v/>
+        <v>Un muerto es un anclaje fijo que se utiliza para amarrar embarcaciones en puertos o zonas de fondeo. Este sistema permite que las embarcaciones permanezcan seguras y estables, evitando que se desplacen con las corrientes o el viento.</v>
       </c>
       <c r="O10" t="str">
-        <v/>
+        <v>El término "muerto" en náutica se refiere a un punto de amarre fijo, como un noray, donde se puede asegurar un barco. Este sistema de amarre es fundamental para mantener la embarcación en su lugar y evitar que se desplace por la acción del viento o las corrientes.</v>
       </c>
       <c r="P10" t="str">
-        <v/>
+        <v>Un "muerto" es un anclaje fijo que se utiliza para amarrar embarcaciones en un lugar determinado, asegurando que no se desplace con las corrientes o el viento. Este sistema es fundamental para mantener la estabilidad y seguridad de las embarcaciones en puertos o fondeaderos.</v>
       </c>
     </row>
     <row r="11">
@@ -987,16 +987,16 @@
         <v>Decoraciones rústicas realizadas en determinados buques.</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>Las cornamusas son elementos de fijación en forma de T, generalmente de madera o metal, que se instalan en diferentes partes del barco. Su función principal es permitir el amarre de cabos y drizas, facilitando así la maniobra y el control de las velas y otros elementos del aparejo.</v>
       </c>
       <c r="N12" t="str">
-        <v/>
+        <v>Las cornamusas son elementos de amarre que se utilizan en las embarcaciones para asegurar cabos y otros elementos. Su diseño permite que los cabos se fijen de manera segura, facilitando la maniobra y el control de la embarcación.</v>
       </c>
       <c r="O12" t="str">
-        <v/>
+        <v>Las cornamusas son elementos de amarre que se utilizan en las embarcaciones para asegurar cabos y cuerdas. Su diseño permite que los marineros puedan fijar y liberar los cabos de manera rápida y eficiente, facilitando así las maniobras a bordo.</v>
       </c>
       <c r="P12" t="str">
-        <v/>
+        <v>Las cornamusas son elementos de amarre que se utilizan en los barcos para asegurar las drizas y los cabos. Se encuentran generalmente en el costado de la embarcación y permiten una sujeción rápida y eficiente de las líneas.</v>
       </c>
     </row>
     <row r="13">
@@ -1087,16 +1087,16 @@
         <v>Sobre los portillos para aislarlos del agua de lluvia.</v>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>Las defensas son elementos de protección que se colocan en los costados del barco y en el muelle para prevenir daños por rozamientos o golpes durante el atraque. Su uso es fundamental para garantizar la seguridad de la embarcación y del puerto, evitando así posibles accidentes.</v>
       </c>
       <c r="N14" t="str">
-        <v/>
+        <v>Las defensas son elementos de protección que se colocan en los costados de la embarcación para evitar daños al chocar con otros barcos o con el muelle. Su correcta colocación es fundamental para mantener la integridad de la embarcación durante las maniobras en puerto.</v>
       </c>
       <c r="O14" t="str">
-        <v/>
+        <v>Las defensas son elementos de protección que se colocan en los costados de la embarcación para evitar daños en caso de colisiones o rozaduras con otros barcos o muelles. Su correcta colocación y uso son fundamentales para mantener la integridad de la embarcación durante las maniobras de atraque y desatraque.</v>
       </c>
       <c r="P14" t="str">
-        <v/>
+        <v>Las defensas son elementos utilizados en la navegación para proteger la embarcación de golpes y roces con otros barcos o estructuras. Se colocan en los costados del barco y ayudan a amortiguar el impacto, evitando daños en la estructura del casco.</v>
       </c>
     </row>
     <row r="15">
@@ -1137,16 +1137,16 @@
         <v>Viento de Levante</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>Un noray es un dispositivo de amarre que se utiliza en los puertos y muelles para asegurar embarcaciones. Se trata de un anclaje fijo, generalmente de metal, que permite atar las cuerdas de los barcos y mantenerlos en su lugar.</v>
       </c>
       <c r="N15" t="str">
-        <v/>
+        <v>Un noray es un dispositivo de amarre que se utiliza en puertos y muelles para asegurar embarcaciones. Consiste en un anclaje fijo, generalmente de metal, que permite atar las cuerdas de los barcos y mantenerlos en su lugar.</v>
       </c>
       <c r="O15" t="str">
-        <v/>
+        <v>Un noray es un dispositivo de amarre que se utiliza en los puertos para asegurar las embarcaciones. Consiste en un poste o anclaje que permite atar las cuerdas de los barcos, garantizando su estabilidad y evitando que se desplacen.</v>
       </c>
       <c r="P15" t="str">
-        <v/>
+        <v>Un noray es un dispositivo de amarre que se utiliza en los puertos y en las embarcaciones para asegurar las líneas de fondeo. Generalmente, se trata de un anclaje fijo en el muelle o en el fondo marino, que permite mantener la embarcación en su lugar.</v>
       </c>
     </row>
     <row r="16">
@@ -1187,16 +1187,16 @@
         <v>Aprisionar la cadena del buque y así evitar que se file.</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>El orinque es una cuerda o cadena que se utiliza para señalar la ubicación de la ancla fondeada, permitiendo a los navegantes identificar fácilmente su posición y evitar que la embarcación se desplace. Su correcta utilización es fundamental para mantener la seguridad y la estabilidad de la embarcación en el fondeo.</v>
       </c>
       <c r="N16" t="str">
-        <v/>
+        <v>El 'orinque' es un cabo que se utiliza para asegurar la embarcación a un punto fijo, como un muelle o una boya, evitando que se desplace con el viento o la corriente. Su correcta utilización es fundamental para mantener la estabilidad y seguridad del barco en puerto.</v>
       </c>
       <c r="O16" t="str">
-        <v/>
+        <v>El 'orinque' es un cabo que se utiliza para asegurar el aparejo de un buque, permitiendo mantener la estabilidad y el control de las velas. Su correcta utilización es fundamental para el buen funcionamiento de la navegación a vela.</v>
       </c>
       <c r="P16" t="str">
-        <v/>
+        <v>El orinque es un cabo que se utiliza para asegurar la cadena del ancla, evitando que esta se desplace o se enrede, lo que podría dificultar la maniobra de fondeo. Su correcta utilización es fundamental para mantener la estabilidad del buque en el fondeo.</v>
       </c>
     </row>
     <row r="17">
@@ -1437,16 +1437,16 @@
         <v>Chocar con algo que flote.</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>Garrear se refiere a la situación en la que el ancla se desplaza por el fondo marino, lo que puede ocurrir debido a condiciones de viento o corriente que superan la capacidad de sujeción del ancla. Es importante reconocer este fenómeno para evitar que la embarcación se desplace de manera no controlada.</v>
       </c>
       <c r="N21" t="str">
-        <v/>
+        <v>Garrear se refiere a la situación en la que una embarcación se desplaza alrededor de su ancla debido a la falta de sujeción adecuada, lo que puede ser peligroso en condiciones de viento o corriente. Es importante asegurarse de que el ancla esté bien fijada para evitar este problema y mantener la embarcación en su posición deseada.</v>
       </c>
       <c r="O21" t="str">
-        <v/>
+        <v>Garrear se refiere a la acción de hacer que el casco de una embarcación roce con el muelle durante el atraque o desatraque. Este fenómeno puede causar daños tanto en la embarcación como en la infraestructura del muelle, por lo que es importante realizar maniobras con cuidado para evitarlo.</v>
       </c>
       <c r="P21" t="str">
-        <v/>
+        <v>Garrear se refiere a la acción de que una embarcación se desplace de manera incontrolada, generalmente debido a la falta de anclaje adecuado o a la influencia de corrientes y vientos. Este fenómeno puede llevar a que la embarcación colisione con otros objetos flotantes o estructuras, lo que puede resultar en daños.</v>
       </c>
     </row>
     <row r="22">
@@ -1587,16 +1587,16 @@
         <v>Chocar con algo que flote.</v>
       </c>
       <c r="M24" t="str">
-        <v/>
+        <v>Garrear se refiere a la situación en la que el ancla de una embarcación se desplaza por el fondo marino, lo que puede comprometer la seguridad de la nave al no mantenerla en su posición deseada. Este fenómeno puede ocurrir debido a condiciones meteorológicas adversas o a un anclaje inadecuado.</v>
       </c>
       <c r="N24" t="str">
-        <v/>
+        <v>Garrear se refiere a la situación en la que una embarcación se desplaza alrededor de su ancla debido a la falta de sujeción adecuada, lo que puede ser peligroso en condiciones de viento o corriente. Es importante asegurarse de que el ancla esté bien fijada para evitar este problema y mantener la embarcación en su posición deseada.</v>
       </c>
       <c r="O24" t="str">
-        <v/>
+        <v>Garrear se refiere a la acción de que el casco de una embarcación roce con el muelle o el fondo, lo que puede causar daños en la estructura del barco. Es importante evitar esta situación para mantener la integridad del casco y asegurar la seguridad de la navegación.</v>
       </c>
       <c r="P24" t="str">
-        <v/>
+        <v>Garrear se refiere a la acción de que una embarcación se desplace de manera incontrolada, generalmente debido a la falta de anclaje adecuado, lo que puede llevar a que la embarcación se desplace hacia otros objetos o embarcaciones. Este fenómeno puede ser peligroso, ya que puede causar colisiones o daños a la embarcación y a otros elementos en el agua.</v>
       </c>
     </row>
     <row r="25">
